--- a/Template Gantt.xlsx
+++ b/Template Gantt.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65AE309E-3472-2A4B-95B0-82FE01FF02C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{65AE309E-3472-2A4B-95B0-82FE01FF02C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{000A0124-34FD-45FB-A1B3-3D768FADF08C}"/>
   <bookViews>
-    <workbookView xWindow="3440" yWindow="0" windowWidth="25360" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projektplan" sheetId="11" r:id="rId1"/>
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="Anzeigewoche">Projektplan!$E$4</definedName>
+    <definedName name="Heute" localSheetId="0">TODAY()</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Projektplan!$4:$6</definedName>
-    <definedName name="Heute" localSheetId="0">TODAY()</definedName>
     <definedName name="Projektanfang">Projektplan!$E$3</definedName>
     <definedName name="task_end" localSheetId="0">Projektplan!$F1</definedName>
     <definedName name="task_progress" localSheetId="0">Projektplan!$D1</definedName>
@@ -1045,7 +1045,7 @@
     <xf numFmtId="0" fontId="9" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1291,86 +1291,84 @@
     <xf numFmtId="172" fontId="11" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="54">
-    <cellStyle name="20 % - Akzent1" xfId="31" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent2" xfId="35" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent3" xfId="39" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent4" xfId="43" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent5" xfId="47" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20 % - Akzent6" xfId="51" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent1" xfId="32" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent2" xfId="36" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent3" xfId="40" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent4" xfId="44" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent5" xfId="48" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40 % - Akzent6" xfId="52" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent1" xfId="33" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent2" xfId="37" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent3" xfId="41" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent4" xfId="45" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent5" xfId="49" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60 % - Akzent6" xfId="53" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Akzent1" xfId="30" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Akzent2" xfId="34" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Akzent3" xfId="38" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Akzent4" xfId="42" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Akzent5" xfId="46" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Akzent6" xfId="50" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="20% - Accent1" xfId="31" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="43" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="47" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="51" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="32" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="36" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="40" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="44" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="48" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="52" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="41" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="45" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="49" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="53" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="30" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="42" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="46" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="50" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Aufgabe" xfId="12" xr:uid="{6391D789-272B-4DD2-9BF3-2CDCF610FA41}"/>
-    <cellStyle name="Ausgabe" xfId="22" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Berechnung" xfId="23" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Besuchter Hyperlink" xfId="13" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="23" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="25" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="14" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="15" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Currency [0]" xfId="16" builtinId="7" customBuiltin="1"/>
     <cellStyle name="Datum" xfId="10" xr:uid="{229918B6-DD13-4F5A-97B9-305F7E002AA3}"/>
-    <cellStyle name="Dezimal [0]" xfId="14" builtinId="6" customBuiltin="1"/>
-    <cellStyle name="Eingabe" xfId="21" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Ergebnis" xfId="29" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Erklärender Text" xfId="28" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Gut" xfId="18" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Komma" xfId="4" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="Link" xfId="1" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="28" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="13" builtinId="9" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="18" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="6" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="7" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="8" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="17" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="21" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="24" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Name" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="Neutral" xfId="20" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Notiz" xfId="27" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="27" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="22" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5" customBuiltin="1"/>
     <cellStyle name="Projektanfang" xfId="9" xr:uid="{8EB8A09A-C31C-40A3-B2C1-9449520178B8}"/>
-    <cellStyle name="Prozent" xfId="2" builtinId="5" customBuiltin="1"/>
-    <cellStyle name="Schlecht" xfId="19" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Überschrift" xfId="5" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Überschrift 1" xfId="6" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Überschrift 2" xfId="7" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Überschrift 3" xfId="8" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Überschrift 4" xfId="17" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Verknüpfte Zelle" xfId="24" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Währung" xfId="15" builtinId="4" customBuiltin="1"/>
-    <cellStyle name="Währung [0]" xfId="16" builtinId="7" customBuiltin="1"/>
-    <cellStyle name="Warnender Text" xfId="26" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="29" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="26" builtinId="11" customBuiltin="1"/>
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
-    <cellStyle name="Zelle überprüfen" xfId="25" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -1663,7 +1661,10 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:endParaRPr lang="de-DE" sz="1100"/>
+          <a:r>
+            <a:rPr lang="de-DE" sz="2400"/>
+            <a:t>Meteostation</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1995,21 +1996,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BL36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="45" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
-    <col min="8" max="8" width="6.1640625" hidden="1" customWidth="1"/>
-    <col min="9" max="64" width="2.5" customWidth="1"/>
-    <col min="69" max="70" width="10.33203125"/>
+    <col min="1" max="1" width="2.6328125" style="45" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" customWidth="1"/>
+    <col min="8" max="8" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="9" max="64" width="2.453125" customWidth="1"/>
+    <col min="69" max="70" width="10.36328125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
@@ -2020,66 +2021,50 @@
       <c r="D1" s="2"/>
       <c r="E1" s="4"/>
       <c r="F1" s="34"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="96" t="s">
+      <c r="H1" s="2"/>
+      <c r="I1" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
     </row>
-    <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="93"/>
       <c r="I2" s="67"/>
     </row>
-    <row r="3" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="45" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="87" t="s">
+      <c r="C3" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="88"/>
+      <c r="D3" s="94"/>
       <c r="E3" s="92">
-        <f ca="1">TODAY()</f>
-        <v>44992</v>
+        <v>46280</v>
       </c>
       <c r="F3" s="92"/>
     </row>
-    <row r="4" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="87" t="s">
+      <c r="C4" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="88"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="7">
         <v>1</v>
       </c>
       <c r="I4" s="89">
-        <f ca="1">I5</f>
-        <v>44991</v>
+        <f>I5</f>
+        <v>46279</v>
       </c>
       <c r="J4" s="90"/>
       <c r="K4" s="90"/>
@@ -2088,8 +2073,8 @@
       <c r="N4" s="90"/>
       <c r="O4" s="91"/>
       <c r="P4" s="89">
-        <f ca="1">P5</f>
-        <v>44998</v>
+        <f>P5</f>
+        <v>46286</v>
       </c>
       <c r="Q4" s="90"/>
       <c r="R4" s="90"/>
@@ -2098,8 +2083,8 @@
       <c r="U4" s="90"/>
       <c r="V4" s="91"/>
       <c r="W4" s="89">
-        <f ca="1">W5</f>
-        <v>45005</v>
+        <f>W5</f>
+        <v>46293</v>
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="90"/>
@@ -2108,8 +2093,8 @@
       <c r="AB4" s="90"/>
       <c r="AC4" s="91"/>
       <c r="AD4" s="89">
-        <f ca="1">AD5</f>
-        <v>45012</v>
+        <f>AD5</f>
+        <v>46300</v>
       </c>
       <c r="AE4" s="90"/>
       <c r="AF4" s="90"/>
@@ -2118,8 +2103,8 @@
       <c r="AI4" s="90"/>
       <c r="AJ4" s="91"/>
       <c r="AK4" s="89">
-        <f ca="1">AK5</f>
-        <v>45019</v>
+        <f>AK5</f>
+        <v>46307</v>
       </c>
       <c r="AL4" s="90"/>
       <c r="AM4" s="90"/>
@@ -2128,8 +2113,8 @@
       <c r="AP4" s="90"/>
       <c r="AQ4" s="91"/>
       <c r="AR4" s="89">
-        <f ca="1">AR5</f>
-        <v>45026</v>
+        <f>AR5</f>
+        <v>46314</v>
       </c>
       <c r="AS4" s="90"/>
       <c r="AT4" s="90"/>
@@ -2138,8 +2123,8 @@
       <c r="AW4" s="90"/>
       <c r="AX4" s="91"/>
       <c r="AY4" s="89">
-        <f ca="1">AY5</f>
-        <v>45033</v>
+        <f>AY5</f>
+        <v>46321</v>
       </c>
       <c r="AZ4" s="90"/>
       <c r="BA4" s="90"/>
@@ -2148,8 +2133,8 @@
       <c r="BD4" s="90"/>
       <c r="BE4" s="91"/>
       <c r="BF4" s="89">
-        <f ca="1">BF5</f>
-        <v>45040</v>
+        <f>BF5</f>
+        <v>46328</v>
       </c>
       <c r="BG4" s="90"/>
       <c r="BH4" s="90"/>
@@ -2158,249 +2143,248 @@
       <c r="BK4" s="90"/>
       <c r="BL4" s="91"/>
     </row>
-    <row r="5" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="46" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="66"/>
-      <c r="C5" s="93"/>
       <c r="D5" s="66"/>
       <c r="E5" s="66"/>
       <c r="F5" s="66"/>
       <c r="G5" s="66"/>
       <c r="I5" s="84">
-        <f ca="1">Projektanfang-WEEKDAY(Projektanfang,1)+2+7*(Anzeigewoche-1)</f>
-        <v>44991</v>
+        <f>Projektanfang-WEEKDAY(Projektanfang,1)+2+7*(Anzeigewoche-1)</f>
+        <v>46279</v>
       </c>
       <c r="J5" s="85">
-        <f ca="1">I5+1</f>
-        <v>44992</v>
+        <f>I5+1</f>
+        <v>46280</v>
       </c>
       <c r="K5" s="85">
-        <f t="shared" ref="K5:AX5" ca="1" si="0">J5+1</f>
-        <v>44993</v>
+        <f t="shared" ref="K5:AX5" si="0">J5+1</f>
+        <v>46281</v>
       </c>
       <c r="L5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>44994</v>
+        <f t="shared" si="0"/>
+        <v>46282</v>
       </c>
       <c r="M5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>44995</v>
+        <f t="shared" si="0"/>
+        <v>46283</v>
       </c>
       <c r="N5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>44996</v>
+        <f t="shared" si="0"/>
+        <v>46284</v>
       </c>
       <c r="O5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>44997</v>
+        <f t="shared" si="0"/>
+        <v>46285</v>
       </c>
       <c r="P5" s="84">
-        <f ca="1">O5+1</f>
-        <v>44998</v>
+        <f>O5+1</f>
+        <v>46286</v>
       </c>
       <c r="Q5" s="85">
-        <f ca="1">P5+1</f>
-        <v>44999</v>
+        <f>P5+1</f>
+        <v>46287</v>
       </c>
       <c r="R5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45000</v>
+        <f t="shared" si="0"/>
+        <v>46288</v>
       </c>
       <c r="S5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45001</v>
+        <f t="shared" si="0"/>
+        <v>46289</v>
       </c>
       <c r="T5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45002</v>
+        <f t="shared" si="0"/>
+        <v>46290</v>
       </c>
       <c r="U5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45003</v>
+        <f t="shared" si="0"/>
+        <v>46291</v>
       </c>
       <c r="V5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>45004</v>
+        <f t="shared" si="0"/>
+        <v>46292</v>
       </c>
       <c r="W5" s="84">
-        <f ca="1">V5+1</f>
-        <v>45005</v>
+        <f>V5+1</f>
+        <v>46293</v>
       </c>
       <c r="X5" s="85">
-        <f ca="1">W5+1</f>
-        <v>45006</v>
+        <f>W5+1</f>
+        <v>46294</v>
       </c>
       <c r="Y5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45007</v>
+        <f t="shared" si="0"/>
+        <v>46295</v>
       </c>
       <c r="Z5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45008</v>
+        <f t="shared" si="0"/>
+        <v>46296</v>
       </c>
       <c r="AA5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45009</v>
+        <f t="shared" si="0"/>
+        <v>46297</v>
       </c>
       <c r="AB5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45010</v>
+        <f t="shared" si="0"/>
+        <v>46298</v>
       </c>
       <c r="AC5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>45011</v>
+        <f t="shared" si="0"/>
+        <v>46299</v>
       </c>
       <c r="AD5" s="84">
-        <f ca="1">AC5+1</f>
-        <v>45012</v>
+        <f>AC5+1</f>
+        <v>46300</v>
       </c>
       <c r="AE5" s="85">
-        <f ca="1">AD5+1</f>
-        <v>45013</v>
+        <f>AD5+1</f>
+        <v>46301</v>
       </c>
       <c r="AF5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45014</v>
+        <f t="shared" si="0"/>
+        <v>46302</v>
       </c>
       <c r="AG5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45015</v>
+        <f t="shared" si="0"/>
+        <v>46303</v>
       </c>
       <c r="AH5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45016</v>
+        <f t="shared" si="0"/>
+        <v>46304</v>
       </c>
       <c r="AI5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45017</v>
+        <f t="shared" si="0"/>
+        <v>46305</v>
       </c>
       <c r="AJ5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>45018</v>
+        <f t="shared" si="0"/>
+        <v>46306</v>
       </c>
       <c r="AK5" s="84">
-        <f ca="1">AJ5+1</f>
-        <v>45019</v>
+        <f>AJ5+1</f>
+        <v>46307</v>
       </c>
       <c r="AL5" s="85">
-        <f ca="1">AK5+1</f>
-        <v>45020</v>
+        <f>AK5+1</f>
+        <v>46308</v>
       </c>
       <c r="AM5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45021</v>
+        <f t="shared" si="0"/>
+        <v>46309</v>
       </c>
       <c r="AN5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45022</v>
+        <f t="shared" si="0"/>
+        <v>46310</v>
       </c>
       <c r="AO5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45023</v>
+        <f t="shared" si="0"/>
+        <v>46311</v>
       </c>
       <c r="AP5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45024</v>
+        <f t="shared" si="0"/>
+        <v>46312</v>
       </c>
       <c r="AQ5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>45025</v>
+        <f t="shared" si="0"/>
+        <v>46313</v>
       </c>
       <c r="AR5" s="84">
-        <f ca="1">AQ5+1</f>
-        <v>45026</v>
+        <f>AQ5+1</f>
+        <v>46314</v>
       </c>
       <c r="AS5" s="85">
-        <f ca="1">AR5+1</f>
-        <v>45027</v>
+        <f>AR5+1</f>
+        <v>46315</v>
       </c>
       <c r="AT5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45028</v>
+        <f t="shared" si="0"/>
+        <v>46316</v>
       </c>
       <c r="AU5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45029</v>
+        <f t="shared" si="0"/>
+        <v>46317</v>
       </c>
       <c r="AV5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45030</v>
+        <f t="shared" si="0"/>
+        <v>46318</v>
       </c>
       <c r="AW5" s="85">
-        <f t="shared" ca="1" si="0"/>
-        <v>45031</v>
+        <f t="shared" si="0"/>
+        <v>46319</v>
       </c>
       <c r="AX5" s="86">
-        <f t="shared" ca="1" si="0"/>
-        <v>45032</v>
+        <f t="shared" si="0"/>
+        <v>46320</v>
       </c>
       <c r="AY5" s="84">
-        <f ca="1">AX5+1</f>
-        <v>45033</v>
+        <f>AX5+1</f>
+        <v>46321</v>
       </c>
       <c r="AZ5" s="85">
-        <f ca="1">AY5+1</f>
-        <v>45034</v>
+        <f>AY5+1</f>
+        <v>46322</v>
       </c>
       <c r="BA5" s="85">
-        <f t="shared" ref="BA5:BE5" ca="1" si="1">AZ5+1</f>
-        <v>45035</v>
+        <f t="shared" ref="BA5:BE5" si="1">AZ5+1</f>
+        <v>46323</v>
       </c>
       <c r="BB5" s="85">
-        <f t="shared" ca="1" si="1"/>
-        <v>45036</v>
+        <f t="shared" si="1"/>
+        <v>46324</v>
       </c>
       <c r="BC5" s="85">
-        <f t="shared" ca="1" si="1"/>
-        <v>45037</v>
+        <f t="shared" si="1"/>
+        <v>46325</v>
       </c>
       <c r="BD5" s="85">
-        <f t="shared" ca="1" si="1"/>
-        <v>45038</v>
+        <f t="shared" si="1"/>
+        <v>46326</v>
       </c>
       <c r="BE5" s="86">
-        <f t="shared" ca="1" si="1"/>
-        <v>45039</v>
+        <f t="shared" si="1"/>
+        <v>46327</v>
       </c>
       <c r="BF5" s="84">
-        <f ca="1">BE5+1</f>
-        <v>45040</v>
+        <f>BE5+1</f>
+        <v>46328</v>
       </c>
       <c r="BG5" s="85">
-        <f ca="1">BF5+1</f>
-        <v>45041</v>
+        <f>BF5+1</f>
+        <v>46329</v>
       </c>
       <c r="BH5" s="85">
-        <f t="shared" ref="BH5:BL5" ca="1" si="2">BG5+1</f>
-        <v>45042</v>
+        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
+        <v>46330</v>
       </c>
       <c r="BI5" s="85">
-        <f t="shared" ca="1" si="2"/>
-        <v>45043</v>
+        <f t="shared" si="2"/>
+        <v>46331</v>
       </c>
       <c r="BJ5" s="85">
-        <f t="shared" ca="1" si="2"/>
-        <v>45044</v>
+        <f t="shared" si="2"/>
+        <v>46332</v>
       </c>
       <c r="BK5" s="85">
-        <f t="shared" ca="1" si="2"/>
-        <v>45045</v>
+        <f t="shared" si="2"/>
+        <v>46333</v>
       </c>
       <c r="BL5" s="86">
-        <f t="shared" ca="1" si="2"/>
-        <v>45046</v>
+        <f t="shared" si="2"/>
+        <v>46334</v>
       </c>
     </row>
-    <row r="6" spans="1:64" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:64" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="46" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="94" t="s">
+      <c r="C6" s="87" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="9" t="s">
@@ -2417,231 +2401,231 @@
         <v>36</v>
       </c>
       <c r="I6" s="10" t="str">
-        <f t="shared" ref="I6:AN6" ca="1" si="3">LEFT(TEXT(I5,"TTT"),1)</f>
+        <f t="shared" ref="I6:AN6" si="3">LEFT(TEXT(I5,"TTT"),1)</f>
         <v>M</v>
       </c>
       <c r="J6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="K6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="L6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="M6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="O6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="P6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="Q6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="R6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="S6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="T6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="U6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="V6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="W6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="X6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="Y6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="Z6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="AA6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AB6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AC6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AD6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AE6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="AF6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AG6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="AH6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>F</v>
       </c>
       <c r="AI6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AJ6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
       <c r="AK6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AL6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="AM6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
       <c r="AN6" s="10" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="AO6" s="10" t="str">
-        <f t="shared" ref="AO6:BT6" ca="1" si="4">LEFT(TEXT(AO5,"TTT"),1)</f>
+        <f t="shared" ref="AO6:BL6" si="4">LEFT(TEXT(AO5,"TTT"),1)</f>
         <v>F</v>
       </c>
       <c r="AP6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AQ6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AR6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="AS6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="AT6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="AU6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="AV6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="AW6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AX6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="AY6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="AZ6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="BA6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="BB6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="BC6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="BD6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BE6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BF6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="BG6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="BH6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
       <c r="BI6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
       <c r="BJ6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>F</v>
       </c>
       <c r="BK6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
       <c r="BL6" s="10" t="str">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
     </row>
-    <row r="7" spans="1:64" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:64" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="45" t="s">
         <v>6</v>
       </c>
@@ -2708,7 +2692,7 @@
       <c r="BK7" s="31"/>
       <c r="BL7" s="31"/>
     </row>
-    <row r="8" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="46" t="s">
         <v>7</v>
       </c>
@@ -2781,7 +2765,7 @@
       <c r="BK8" s="31"/>
       <c r="BL8" s="31"/>
     </row>
-    <row r="9" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="46" t="s">
         <v>8</v>
       </c>
@@ -2795,16 +2779,16 @@
         <v>0.5</v>
       </c>
       <c r="E9" s="71">
-        <f ca="1">Projektanfang</f>
-        <v>44992</v>
+        <f>Projektanfang</f>
+        <v>46280</v>
       </c>
       <c r="F9" s="71">
-        <f ca="1">E9+3</f>
-        <v>44995</v>
+        <f>E9+3</f>
+        <v>46283</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I9" s="31"/>
@@ -2864,7 +2848,7 @@
       <c r="BK9" s="31"/>
       <c r="BL9" s="31"/>
     </row>
-    <row r="10" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="46" t="s">
         <v>9</v>
       </c>
@@ -2876,16 +2860,16 @@
         <v>0.6</v>
       </c>
       <c r="E10" s="71">
-        <f ca="1">F9</f>
-        <v>44995</v>
+        <f>F9</f>
+        <v>46283</v>
       </c>
       <c r="F10" s="71">
-        <f ca="1">E10+2</f>
-        <v>44997</v>
+        <f>E10+2</f>
+        <v>46285</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I10" s="31"/>
@@ -2945,7 +2929,7 @@
       <c r="BK10" s="31"/>
       <c r="BL10" s="31"/>
     </row>
-    <row r="11" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="45"/>
       <c r="B11" s="61" t="s">
         <v>21</v>
@@ -2955,16 +2939,16 @@
         <v>0.5</v>
       </c>
       <c r="E11" s="71">
-        <f ca="1">F10</f>
-        <v>44997</v>
+        <f>F10</f>
+        <v>46285</v>
       </c>
       <c r="F11" s="71">
-        <f ca="1">E11+4</f>
-        <v>45001</v>
+        <f>E11+4</f>
+        <v>46289</v>
       </c>
       <c r="G11" s="14"/>
       <c r="H11" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I11" s="31"/>
@@ -3024,7 +3008,7 @@
       <c r="BK11" s="31"/>
       <c r="BL11" s="31"/>
     </row>
-    <row r="12" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="45"/>
       <c r="B12" s="61" t="s">
         <v>22</v>
@@ -3034,16 +3018,16 @@
         <v>0.25</v>
       </c>
       <c r="E12" s="71">
-        <f ca="1">F11</f>
-        <v>45001</v>
+        <f>F11</f>
+        <v>46289</v>
       </c>
       <c r="F12" s="71">
-        <f ca="1">E12+5</f>
-        <v>45006</v>
+        <f>E12+5</f>
+        <v>46294</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="I12" s="31"/>
@@ -3103,7 +3087,7 @@
       <c r="BK12" s="31"/>
       <c r="BL12" s="31"/>
     </row>
-    <row r="13" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="45"/>
       <c r="B13" s="61" t="s">
         <v>23</v>
@@ -3111,16 +3095,16 @@
       <c r="C13" s="53"/>
       <c r="D13" s="17"/>
       <c r="E13" s="71">
-        <f ca="1">E10+1</f>
-        <v>44996</v>
+        <f>E10+1</f>
+        <v>46284</v>
       </c>
       <c r="F13" s="71">
-        <f ca="1">E13+2</f>
-        <v>44998</v>
+        <f>E13+2</f>
+        <v>46286</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I13" s="31"/>
@@ -3180,7 +3164,7 @@
       <c r="BK13" s="31"/>
       <c r="BL13" s="31"/>
     </row>
-    <row r="14" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="46" t="s">
         <v>10</v>
       </c>
@@ -3253,7 +3237,7 @@
       <c r="BK14" s="31"/>
       <c r="BL14" s="31"/>
     </row>
-    <row r="15" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="46"/>
       <c r="B15" s="62" t="s">
         <v>19</v>
@@ -3263,16 +3247,16 @@
         <v>0.5</v>
       </c>
       <c r="E15" s="74">
-        <f ca="1">E13+1</f>
-        <v>44997</v>
+        <f>E13+1</f>
+        <v>46285</v>
       </c>
       <c r="F15" s="74">
-        <f ca="1">E15+4</f>
-        <v>45001</v>
+        <f>E15+4</f>
+        <v>46289</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I15" s="31"/>
@@ -3332,7 +3316,7 @@
       <c r="BK15" s="31"/>
       <c r="BL15" s="31"/>
     </row>
-    <row r="16" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="45"/>
       <c r="B16" s="62" t="s">
         <v>20</v>
@@ -3342,16 +3326,16 @@
         <v>0.5</v>
       </c>
       <c r="E16" s="74">
-        <f ca="1">E15+2</f>
-        <v>44999</v>
+        <f>E15+2</f>
+        <v>46287</v>
       </c>
       <c r="F16" s="74">
-        <f ca="1">E16+5</f>
-        <v>45004</v>
+        <f>E16+5</f>
+        <v>46292</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="I16" s="31"/>
@@ -3411,7 +3395,7 @@
       <c r="BK16" s="31"/>
       <c r="BL16" s="31"/>
     </row>
-    <row r="17" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="45"/>
       <c r="B17" s="62" t="s">
         <v>21</v>
@@ -3419,16 +3403,16 @@
       <c r="C17" s="55"/>
       <c r="D17" s="20"/>
       <c r="E17" s="74">
-        <f ca="1">F16</f>
-        <v>45004</v>
+        <f>F16</f>
+        <v>46292</v>
       </c>
       <c r="F17" s="74">
-        <f ca="1">E17+3</f>
-        <v>45007</v>
+        <f>E17+3</f>
+        <v>46295</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I17" s="31"/>
@@ -3488,7 +3472,7 @@
       <c r="BK17" s="31"/>
       <c r="BL17" s="31"/>
     </row>
-    <row r="18" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="45"/>
       <c r="B18" s="62" t="s">
         <v>22</v>
@@ -3496,16 +3480,16 @@
       <c r="C18" s="55"/>
       <c r="D18" s="20"/>
       <c r="E18" s="74">
-        <f ca="1">E17</f>
-        <v>45004</v>
+        <f>E17</f>
+        <v>46292</v>
       </c>
       <c r="F18" s="74">
-        <f ca="1">E18+2</f>
-        <v>45006</v>
+        <f>E18+2</f>
+        <v>46294</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I18" s="31"/>
@@ -3565,7 +3549,7 @@
       <c r="BK18" s="31"/>
       <c r="BL18" s="31"/>
     </row>
-    <row r="19" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="45"/>
       <c r="B19" s="62" t="s">
         <v>23</v>
@@ -3573,16 +3557,16 @@
       <c r="C19" s="55"/>
       <c r="D19" s="20"/>
       <c r="E19" s="74">
-        <f ca="1">E18</f>
-        <v>45004</v>
+        <f>E18</f>
+        <v>46292</v>
       </c>
       <c r="F19" s="74">
-        <f ca="1">E19+3</f>
-        <v>45007</v>
+        <f>E19+3</f>
+        <v>46295</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="I19" s="31"/>
@@ -3642,7 +3626,7 @@
       <c r="BK19" s="31"/>
       <c r="BL19" s="31"/>
     </row>
-    <row r="20" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="45" t="s">
         <v>11</v>
       </c>
@@ -3715,7 +3699,7 @@
       <c r="BK20" s="31"/>
       <c r="BL20" s="31"/>
     </row>
-    <row r="21" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="45"/>
       <c r="B21" s="63" t="s">
         <v>19</v>
@@ -3723,16 +3707,16 @@
       <c r="C21" s="57"/>
       <c r="D21" s="23"/>
       <c r="E21" s="77">
-        <f ca="1">E9+15</f>
-        <v>45007</v>
+        <f>E9+15</f>
+        <v>46295</v>
       </c>
       <c r="F21" s="77">
-        <f ca="1">E21+5</f>
-        <v>45012</v>
+        <f>E21+5</f>
+        <v>46300</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="I21" s="31"/>
@@ -3792,7 +3776,7 @@
       <c r="BK21" s="31"/>
       <c r="BL21" s="31"/>
     </row>
-    <row r="22" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="45"/>
       <c r="B22" s="63" t="s">
         <v>20</v>
@@ -3800,16 +3784,16 @@
       <c r="C22" s="57"/>
       <c r="D22" s="23"/>
       <c r="E22" s="77">
-        <f ca="1">F21+1</f>
-        <v>45013</v>
+        <f>F21+1</f>
+        <v>46301</v>
       </c>
       <c r="F22" s="77">
-        <f ca="1">E22+4</f>
-        <v>45017</v>
+        <f>E22+4</f>
+        <v>46305</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I22" s="31"/>
@@ -3869,7 +3853,7 @@
       <c r="BK22" s="31"/>
       <c r="BL22" s="31"/>
     </row>
-    <row r="23" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="45"/>
       <c r="B23" s="63" t="s">
         <v>21</v>
@@ -3877,16 +3861,16 @@
       <c r="C23" s="57"/>
       <c r="D23" s="23"/>
       <c r="E23" s="77">
-        <f ca="1">E22+5</f>
-        <v>45018</v>
+        <f>E22+5</f>
+        <v>46306</v>
       </c>
       <c r="F23" s="77">
-        <f ca="1">E23+5</f>
-        <v>45023</v>
+        <f>E23+5</f>
+        <v>46311</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="I23" s="31"/>
@@ -3946,7 +3930,7 @@
       <c r="BK23" s="31"/>
       <c r="BL23" s="31"/>
     </row>
-    <row r="24" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="45"/>
       <c r="B24" s="63" t="s">
         <v>22</v>
@@ -3954,16 +3938,16 @@
       <c r="C24" s="57"/>
       <c r="D24" s="23"/>
       <c r="E24" s="77">
-        <f ca="1">F23+1</f>
-        <v>45024</v>
+        <f>F23+1</f>
+        <v>46312</v>
       </c>
       <c r="F24" s="77">
-        <f ca="1">E24+4</f>
-        <v>45028</v>
+        <f>E24+4</f>
+        <v>46316</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I24" s="31"/>
@@ -4023,7 +4007,7 @@
       <c r="BK24" s="31"/>
       <c r="BL24" s="31"/>
     </row>
-    <row r="25" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="45"/>
       <c r="B25" s="63" t="s">
         <v>23</v>
@@ -4031,16 +4015,16 @@
       <c r="C25" s="57"/>
       <c r="D25" s="23"/>
       <c r="E25" s="77">
-        <f ca="1">E23</f>
-        <v>45018</v>
+        <f>E23</f>
+        <v>46306</v>
       </c>
       <c r="F25" s="77">
-        <f ca="1">E25+4</f>
-        <v>45022</v>
+        <f>E25+4</f>
+        <v>46310</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="I25" s="31"/>
@@ -4100,7 +4084,7 @@
       <c r="BK25" s="31"/>
       <c r="BL25" s="31"/>
     </row>
-    <row r="26" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="45" t="s">
         <v>11</v>
       </c>
@@ -4173,7 +4157,7 @@
       <c r="BK26" s="31"/>
       <c r="BL26" s="31"/>
     </row>
-    <row r="27" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="45"/>
       <c r="B27" s="64" t="s">
         <v>19</v>
@@ -4248,7 +4232,7 @@
       <c r="BK27" s="31"/>
       <c r="BL27" s="31"/>
     </row>
-    <row r="28" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="45"/>
       <c r="B28" s="64" t="s">
         <v>20</v>
@@ -4323,7 +4307,7 @@
       <c r="BK28" s="31"/>
       <c r="BL28" s="31"/>
     </row>
-    <row r="29" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="45"/>
       <c r="B29" s="64" t="s">
         <v>21</v>
@@ -4398,7 +4382,7 @@
       <c r="BK29" s="31"/>
       <c r="BL29" s="31"/>
     </row>
-    <row r="30" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="45"/>
       <c r="B30" s="64" t="s">
         <v>22</v>
@@ -4473,7 +4457,7 @@
       <c r="BK30" s="31"/>
       <c r="BL30" s="31"/>
     </row>
-    <row r="31" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="45"/>
       <c r="B31" s="64" t="s">
         <v>23</v>
@@ -4548,7 +4532,7 @@
       <c r="BK31" s="31"/>
       <c r="BL31" s="31"/>
     </row>
-    <row r="32" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="45" t="s">
         <v>12</v>
       </c>
@@ -4619,7 +4603,7 @@
       <c r="BK32" s="31"/>
       <c r="BL32" s="31"/>
     </row>
-    <row r="33" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:64" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="46" t="s">
         <v>13</v>
       </c>
@@ -4692,29 +4676,29 @@
       <c r="BK33" s="33"/>
       <c r="BL33" s="33"/>
     </row>
-    <row r="34" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C35" s="11"/>
       <c r="F35" s="47"/>
     </row>
-    <row r="36" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:64" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C36" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D33">
     <cfRule type="dataBar" priority="14">
@@ -4788,86 +4772,86 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="104.6640625" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1640625" style="2"/>
+    <col min="1" max="1" width="104.6328125" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:2" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:2" s="37" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="36"/>
     </row>
-    <row r="3" spans="1:2" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" s="41" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="42"/>
     </row>
-    <row r="4" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.6">
       <c r="A4" s="39" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="74" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="35" customFormat="1" ht="205" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" s="35" customFormat="1" ht="205" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="44" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.6">
       <c r="A8" s="39" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="35" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" s="35" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="43" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.6">
       <c r="A11" s="39" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="35" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" s="35" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="43" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" s="38" customFormat="1" ht="26" x14ac:dyDescent="0.6">
       <c r="A14" s="39" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
         <v>51</v>
       </c>
@@ -4906,6 +4890,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5193,15 +5186,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
@@ -5215,6 +5199,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5233,12 +5225,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>